--- a/templates/template_horeca.xlsx
+++ b/templates/template_horeca.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="R241ace5dc9544e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="R33cf603214394ba3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,9 +79,6 @@
     <x:t xml:space="preserve">CAMBODIA COLA</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">IZE PET 300ml Flavour</x:t>
   </x:si>
   <x:si>
@@ -155,9 +152,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BACCHUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dragon</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BACCHUSE Sugar Free</x:t>
@@ -428,7 +422,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R54cee3a3708a43a5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R219c2d57182c4620"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1062,8 +1056,8 @@
       <x:c r="A13" s="3">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="B13" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="C13" s="11"/>
       <x:c r="D13" s="12"/>
@@ -1195,7 +1189,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="11"/>
       <x:c r="D17" s="12"/>
@@ -1228,7 +1222,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="11"/>
       <x:c r="D18" s="12"/>
@@ -1391,7 +1385,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C23" s="11"/>
       <x:c r="D23" s="12"/>
@@ -1424,7 +1418,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="11"/>
       <x:c r="D24" s="12"/>
@@ -1454,7 +1448,7 @@
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="10"/>
       <x:c r="C25" s="10"/>
@@ -1485,85 +1479,85 @@
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D26" s="4" t="s">
+      <x:c r="E26" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E26" s="4" t="s">
+      <x:c r="F26" s="4" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F26" s="4" t="s">
+      <x:c r="G26" s="4" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="G26" s="4" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="H26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J26" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J26" s="4" t="s">
+      <x:c r="K26" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K26" s="4" t="s">
+      <x:c r="L26" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="L26" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="M26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="N26" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O26" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O26" s="4" t="s">
+      <x:c r="P26" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="P26" s="4" t="s">
+      <x:c r="Q26" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q26" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="R26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S26" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T26" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="T26" s="4" t="s">
+      <x:c r="U26" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="U26" s="4" t="s">
+      <x:c r="V26" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="V26" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="W26" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X26" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Y26" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="Y26" s="4" t="s">
+      <x:c r="Z26" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="Z26" s="4" t="s">
+      <x:c r="AA26" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="AA26" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
@@ -1579,21 +1573,21 @@
       <x:c r="F27" s="3"/>
       <x:c r="G27" s="3"/>
       <x:c r="H27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I27" s="3"/>
       <x:c r="J27" s="3"/>
       <x:c r="K27" s="3"/>
       <x:c r="L27" s="3"/>
       <x:c r="M27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N27" s="3"/>
       <x:c r="O27" s="3"/>
       <x:c r="P27" s="3"/>
       <x:c r="Q27" s="3"/>
       <x:c r="R27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S27" s="3"/>
       <x:c r="T27" s="3"/>
@@ -1625,14 +1619,14 @@
       <x:c r="K28" s="3"/>
       <x:c r="L28" s="3"/>
       <x:c r="M28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N28" s="3"/>
       <x:c r="O28" s="3"/>
       <x:c r="P28" s="3"/>
       <x:c r="Q28" s="3"/>
       <x:c r="R28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S28" s="3"/>
       <x:c r="T28" s="3"/>
@@ -1657,28 +1651,28 @@
       <x:c r="F29" s="3"/>
       <x:c r="G29" s="3"/>
       <x:c r="H29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I29" s="3"/>
       <x:c r="J29" s="3"/>
       <x:c r="K29" s="3"/>
       <x:c r="L29" s="3"/>
       <x:c r="M29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N29" s="3"/>
       <x:c r="O29" s="3"/>
       <x:c r="P29" s="3"/>
       <x:c r="Q29" s="3"/>
       <x:c r="R29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="S29" s="3"/>
       <x:c r="T29" s="3"/>
       <x:c r="U29" s="3"/>
       <x:c r="V29" s="3"/>
       <x:c r="W29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="X29" s="3"/>
       <x:c r="Y29" s="3"/>
@@ -1703,7 +1697,7 @@
       <x:c r="K30" s="3"/>
       <x:c r="L30" s="3"/>
       <x:c r="M30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N30" s="3"/>
       <x:c r="O30" s="3"/>
@@ -1725,7 +1719,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C31" s="3"/>
       <x:c r="D31" s="3"/>
@@ -1733,7 +1727,7 @@
       <x:c r="F31" s="3"/>
       <x:c r="G31" s="3"/>
       <x:c r="H31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I31" s="3"/>
       <x:c r="J31" s="3"/>
@@ -1759,8 +1753,8 @@
       <x:c r="A32" s="3">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="B32" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="C32" s="3"/>
       <x:c r="D32" s="3"/>
@@ -1858,7 +1852,7 @@
       <x:c r="P34" s="3"/>
       <x:c r="Q34" s="3"/>
       <x:c r="R34" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S34" s="3"/>
       <x:c r="T34" s="3"/>
@@ -1883,7 +1877,7 @@
       <x:c r="F35" s="3"/>
       <x:c r="G35" s="3"/>
       <x:c r="H35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I35" s="3"/>
       <x:c r="J35" s="3"/>
@@ -1894,8 +1888,8 @@
       <x:c r="O35" s="3"/>
       <x:c r="P35" s="3"/>
       <x:c r="Q35" s="3"/>
-      <x:c r="R35" s="1" t="s">
-        <x:v>49</x:v>
+      <x:c r="R35" s="1" t="str">
+        <x:v>Dragon ORD</x:v>
       </x:c>
       <x:c r="S35" s="3"/>
       <x:c r="T35" s="3"/>
@@ -1920,7 +1914,7 @@
       <x:c r="F36" s="3"/>
       <x:c r="G36" s="3"/>
       <x:c r="H36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I36" s="3"/>
       <x:c r="J36" s="3"/>
@@ -1947,7 +1941,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C37" s="3"/>
       <x:c r="D37" s="3"/>
@@ -1955,7 +1949,7 @@
       <x:c r="F37" s="3"/>
       <x:c r="G37" s="3"/>
       <x:c r="H37" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I37" s="3"/>
       <x:c r="J37" s="3"/>
@@ -1967,7 +1961,7 @@
       <x:c r="P37" s="3"/>
       <x:c r="Q37" s="3"/>
       <x:c r="R37" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S37" s="3"/>
       <x:c r="T37" s="3"/>
@@ -1984,7 +1978,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C38" s="3"/>
       <x:c r="D38" s="3"/>
@@ -1992,14 +1986,14 @@
       <x:c r="F38" s="3"/>
       <x:c r="G38" s="3"/>
       <x:c r="H38" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I38" s="3"/>
       <x:c r="J38" s="3"/>
       <x:c r="K38" s="3"/>
       <x:c r="L38" s="3"/>
       <x:c r="M38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N38" s="3"/>
       <x:c r="O38" s="3"/>
@@ -2036,7 +2030,7 @@
       <x:c r="K39" s="3"/>
       <x:c r="L39" s="3"/>
       <x:c r="M39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N39" s="3"/>
       <x:c r="O39" s="3"/>
@@ -2060,7 +2054,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C40" s="3"/>
       <x:c r="D40" s="3"/>
@@ -2073,14 +2067,14 @@
       <x:c r="K40" s="3"/>
       <x:c r="L40" s="3"/>
       <x:c r="M40" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N40" s="3"/>
       <x:c r="O40" s="3"/>
       <x:c r="P40" s="3"/>
       <x:c r="Q40" s="3"/>
       <x:c r="R40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S40" s="3"/>
       <x:c r="T40" s="3"/>
@@ -2097,7 +2091,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C41" s="3"/>
       <x:c r="D41" s="3"/>
@@ -2105,28 +2099,28 @@
       <x:c r="F41" s="3"/>
       <x:c r="G41" s="3"/>
       <x:c r="H41" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I41" s="3"/>
       <x:c r="J41" s="3"/>
       <x:c r="K41" s="3"/>
       <x:c r="L41" s="3"/>
       <x:c r="M41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N41" s="3"/>
       <x:c r="O41" s="3"/>
       <x:c r="P41" s="3"/>
       <x:c r="Q41" s="3"/>
       <x:c r="R41" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S41" s="3"/>
       <x:c r="T41" s="3"/>
       <x:c r="U41" s="3"/>
       <x:c r="V41" s="3"/>
       <x:c r="W41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="X41" s="3"/>
       <x:c r="Y41" s="3"/>
@@ -2138,7 +2132,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" s="3"/>
       <x:c r="D42" s="3"/>
@@ -2146,28 +2140,28 @@
       <x:c r="F42" s="3"/>
       <x:c r="G42" s="3"/>
       <x:c r="H42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I42" s="3"/>
       <x:c r="J42" s="3"/>
       <x:c r="K42" s="3"/>
       <x:c r="L42" s="3"/>
       <x:c r="M42" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N42" s="3"/>
       <x:c r="O42" s="3"/>
       <x:c r="P42" s="3"/>
       <x:c r="Q42" s="3"/>
       <x:c r="R42" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S42" s="3"/>
       <x:c r="T42" s="3"/>
       <x:c r="U42" s="3"/>
       <x:c r="V42" s="3"/>
       <x:c r="W42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="X42" s="3"/>
       <x:c r="Y42" s="3"/>
@@ -2176,7 +2170,7 @@
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
       <x:c r="A43" s="9" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="9"/>
       <x:c r="C43" s="9"/>
@@ -2186,7 +2180,7 @@
       <x:c r="G43" s="9"/>
       <x:c r="H43" s="21"/>
       <x:c r="I43" s="22" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J43" s="22"/>
       <x:c r="K43" s="22"/>
@@ -2198,7 +2192,7 @@
       <x:c r="Q43" s="22"/>
       <x:c r="R43" s="23"/>
       <x:c r="S43" s="9" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T43" s="24"/>
       <x:c r="U43" s="24"/>
@@ -2256,7 +2250,7 @@
       <x:c r="G45" s="15"/>
       <x:c r="H45" s="23"/>
       <x:c r="I45" s="25" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J45" s="25"/>
       <x:c r="K45" s="25"/>
@@ -2268,7 +2262,7 @@
       <x:c r="Q45" s="25"/>
       <x:c r="R45" s="23"/>
       <x:c r="S45" s="25" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="T45" s="24"/>
       <x:c r="U45" s="24"/>
@@ -2291,7 +2285,7 @@
       <x:c r="G46" s="15"/>
       <x:c r="H46" s="23"/>
       <x:c r="I46" s="25" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J46" s="25"/>
       <x:c r="K46" s="25"/>
@@ -2303,7 +2297,7 @@
       <x:c r="Q46" s="25"/>
       <x:c r="R46" s="23"/>
       <x:c r="S46" s="25" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="T46" s="24"/>
       <x:c r="U46" s="24"/>
@@ -2326,7 +2320,7 @@
       <x:c r="G47" s="15"/>
       <x:c r="H47" s="23"/>
       <x:c r="I47" s="25" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J47" s="25"/>
       <x:c r="K47" s="25"/>
@@ -2338,7 +2332,7 @@
       <x:c r="Q47" s="25"/>
       <x:c r="R47" s="23"/>
       <x:c r="S47" s="25" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="T47" s="24"/>
       <x:c r="U47" s="24"/>
@@ -2489,6 +2483,6 @@
     <x:mergeCell ref="C13:G13"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R692af024af454cd7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fb07424648345e6"/>
 </x:worksheet>
 </file>